--- a/frontend/public/product-excel-en.xlsx
+++ b/frontend/public/product-excel-en.xlsx
@@ -34,7 +34,7 @@
     <t>Average Cycle Time (sec)</t>
   </si>
   <si>
-    <t>Note</t>
+    <t>Notes</t>
   </si>
 </sst>
 </file>
